--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/before_conversion_hessen_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/before_conversion_hessen_mapped_readable.xlsx
@@ -3526,7 +3526,7 @@
     <t>Sand and Gravel</t>
   </si>
   <si>
-    <t>Pelite</t>
+    <t>Claystone</t>
   </si>
   <si>
     <t>Slate</t>
@@ -29935,7 +29935,7 @@
         <v>920</v>
       </c>
       <c r="F321" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G321" t="s">
         <v>1189</v>
@@ -29988,7 +29988,7 @@
         <v>920</v>
       </c>
       <c r="F322" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G322" t="s">
         <v>1189</v>
@@ -30041,7 +30041,7 @@
         <v>921</v>
       </c>
       <c r="F323" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G323" t="s">
         <v>1189</v>
@@ -30109,7 +30109,7 @@
         <v>921</v>
       </c>
       <c r="F324" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G324" t="s">
         <v>1189</v>
@@ -30177,7 +30177,7 @@
         <v>919</v>
       </c>
       <c r="F325" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G325" t="s">
         <v>1189</v>
@@ -30230,7 +30230,7 @@
         <v>919</v>
       </c>
       <c r="F326" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G326" t="s">
         <v>1189</v>
@@ -30283,7 +30283,7 @@
         <v>922</v>
       </c>
       <c r="F327" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G327" t="s">
         <v>1189</v>
@@ -30336,7 +30336,7 @@
         <v>922</v>
       </c>
       <c r="F328" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G328" t="s">
         <v>1189</v>
@@ -30389,7 +30389,7 @@
         <v>922</v>
       </c>
       <c r="F329" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G329" t="s">
         <v>1189</v>
@@ -30436,7 +30436,7 @@
         <v>922</v>
       </c>
       <c r="F330" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G330" t="s">
         <v>1189</v>
@@ -30483,7 +30483,7 @@
         <v>922</v>
       </c>
       <c r="F331" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G331" t="s">
         <v>1189</v>
@@ -30551,7 +30551,7 @@
         <v>922</v>
       </c>
       <c r="F332" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G332" t="s">
         <v>1189</v>
@@ -30619,7 +30619,7 @@
         <v>923</v>
       </c>
       <c r="F333" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G333" t="s">
         <v>1189</v>
@@ -30687,7 +30687,7 @@
         <v>923</v>
       </c>
       <c r="F334" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G334" t="s">
         <v>1189</v>
@@ -30755,7 +30755,7 @@
         <v>923</v>
       </c>
       <c r="F335" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G335" t="s">
         <v>1189</v>
@@ -30784,7 +30784,7 @@
         <v>923</v>
       </c>
       <c r="F336" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G336" t="s">
         <v>1189</v>
@@ -30813,7 +30813,7 @@
         <v>923</v>
       </c>
       <c r="F337" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G337" t="s">
         <v>1189</v>
@@ -30890,7 +30890,7 @@
         <v>923</v>
       </c>
       <c r="F338" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G338" t="s">
         <v>1189</v>
@@ -30967,7 +30967,7 @@
         <v>923</v>
       </c>
       <c r="F339" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G339" t="s">
         <v>1189</v>
@@ -31020,7 +31020,7 @@
         <v>923</v>
       </c>
       <c r="F340" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G340" t="s">
         <v>1189</v>
@@ -31073,7 +31073,7 @@
         <v>923</v>
       </c>
       <c r="F341" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G341" t="s">
         <v>1189</v>
@@ -31159,7 +31159,7 @@
         <v>923</v>
       </c>
       <c r="F342" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G342" t="s">
         <v>1189</v>
@@ -31245,7 +31245,7 @@
         <v>922</v>
       </c>
       <c r="F343" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G343" t="s">
         <v>1189</v>
@@ -31298,7 +31298,7 @@
         <v>922</v>
       </c>
       <c r="F344" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G344" t="s">
         <v>1189</v>
@@ -31351,7 +31351,7 @@
         <v>924</v>
       </c>
       <c r="F345" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G345" t="s">
         <v>1189</v>
@@ -31404,7 +31404,7 @@
         <v>924</v>
       </c>
       <c r="F346" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G346" t="s">
         <v>1189</v>
@@ -31457,7 +31457,7 @@
         <v>925</v>
       </c>
       <c r="F347" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G347" t="s">
         <v>1189</v>
@@ -31510,7 +31510,7 @@
         <v>925</v>
       </c>
       <c r="F348" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G348" t="s">
         <v>1189</v>
@@ -31563,7 +31563,7 @@
         <v>879</v>
       </c>
       <c r="F349" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G349" t="s">
         <v>1189</v>
@@ -31616,7 +31616,7 @@
         <v>879</v>
       </c>
       <c r="F350" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G350" t="s">
         <v>1189</v>
@@ -31669,7 +31669,7 @@
         <v>886</v>
       </c>
       <c r="F351" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G351" t="s">
         <v>1189</v>
@@ -31722,7 +31722,7 @@
         <v>886</v>
       </c>
       <c r="F352" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G352" t="s">
         <v>1189</v>
@@ -31775,7 +31775,7 @@
         <v>926</v>
       </c>
       <c r="F353" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G353" t="s">
         <v>1189</v>
@@ -31828,7 +31828,7 @@
         <v>926</v>
       </c>
       <c r="F354" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G354" t="s">
         <v>1189</v>
@@ -31881,7 +31881,7 @@
         <v>927</v>
       </c>
       <c r="F355" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G355" t="s">
         <v>1189</v>
@@ -31928,7 +31928,7 @@
         <v>927</v>
       </c>
       <c r="F356" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G356" t="s">
         <v>1189</v>
@@ -31975,7 +31975,7 @@
         <v>879</v>
       </c>
       <c r="F357" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G357" t="s">
         <v>1189</v>
@@ -32028,7 +32028,7 @@
         <v>879</v>
       </c>
       <c r="F358" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G358" t="s">
         <v>1189</v>
@@ -32081,7 +32081,7 @@
         <v>928</v>
       </c>
       <c r="F359" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G359" t="s">
         <v>1189</v>
@@ -32146,7 +32146,7 @@
         <v>928</v>
       </c>
       <c r="F360" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G360" t="s">
         <v>1189</v>
@@ -32211,7 +32211,7 @@
         <v>928</v>
       </c>
       <c r="F361" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G361" t="s">
         <v>1189</v>
@@ -32264,7 +32264,7 @@
         <v>928</v>
       </c>
       <c r="F362" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G362" t="s">
         <v>1189</v>
@@ -32317,7 +32317,7 @@
         <v>928</v>
       </c>
       <c r="F363" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G363" t="s">
         <v>1189</v>
@@ -32382,7 +32382,7 @@
         <v>928</v>
       </c>
       <c r="F364" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G364" t="s">
         <v>1189</v>
@@ -32447,7 +32447,7 @@
         <v>928</v>
       </c>
       <c r="F365" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G365" t="s">
         <v>1189</v>
@@ -32476,7 +32476,7 @@
         <v>928</v>
       </c>
       <c r="F366" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G366" t="s">
         <v>1189</v>
@@ -32505,7 +32505,7 @@
         <v>928</v>
       </c>
       <c r="F367" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G367" t="s">
         <v>1189</v>
@@ -32582,7 +32582,7 @@
         <v>928</v>
       </c>
       <c r="F368" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G368" t="s">
         <v>1189</v>
@@ -32659,7 +32659,7 @@
         <v>928</v>
       </c>
       <c r="F369" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G369" t="s">
         <v>1189</v>
@@ -32712,7 +32712,7 @@
         <v>928</v>
       </c>
       <c r="F370" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G370" t="s">
         <v>1189</v>
@@ -32765,7 +32765,7 @@
         <v>928</v>
       </c>
       <c r="F371" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G371" t="s">
         <v>1189</v>
@@ -32851,7 +32851,7 @@
         <v>928</v>
       </c>
       <c r="F372" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G372" t="s">
         <v>1189</v>
@@ -32937,7 +32937,7 @@
         <v>929</v>
       </c>
       <c r="F373" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G373" t="s">
         <v>1189</v>
@@ -33008,7 +33008,7 @@
         <v>929</v>
       </c>
       <c r="F374" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G374" t="s">
         <v>1189</v>
@@ -33079,7 +33079,7 @@
         <v>929</v>
       </c>
       <c r="F375" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G375" t="s">
         <v>1189</v>
@@ -33132,7 +33132,7 @@
         <v>929</v>
       </c>
       <c r="F376" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G376" t="s">
         <v>1189</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/before_conversion_hessen_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/before_conversion_hessen_mapped_readable.xlsx
@@ -3544,7 +3544,7 @@
     <t>Greenschist</t>
   </si>
   <si>
-    <t>Halite</t>
+    <t>Salt</t>
   </si>
   <si>
     <t>Limestone</t>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/before_conversion_hessen_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/HESSEN_Datenbank/before_conversion_hessen_mapped_readable.xlsx
@@ -9841,6 +9841,9 @@
       <c r="AB2">
         <v>31.1</v>
       </c>
+      <c r="AD2">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:31">
       <c r="A3" t="s">
@@ -9888,6 +9891,9 @@
       <c r="X3" t="s">
         <v>863</v>
       </c>
+      <c r="AD3">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:31">
       <c r="A4" t="s">
@@ -9952,6 +9958,9 @@
       </c>
       <c r="AA4" t="s">
         <v>1137</v>
+      </c>
+      <c r="AD4">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:31">
